--- a/app/src/main/java/com/example/methodmesh/modules/nfc/docs/example_odk_protocol_nfc_complete.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/nfc/docs/example_odk_protocol_nfc_complete.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R54904bb1905446ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R38fe55231b114bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R92bdd83ead874b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rb07cb3d372f94904"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rc8ee4777449d4d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rb612de323306498a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -149,21 +149,12 @@
   <x:si>
     <x:t xml:space="preserve">placeholder</x:t>
   </x:si>
-  <x:si>
-    <x:t xml:space="preserve">form_title</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">form_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">protocol_nfc_complete</x:t>
-  </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -174,8 +165,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -187,6 +183,11 @@
         <x:fgColor rgb="FF17324D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E8F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="9">
     <x:border/>
@@ -246,7 +247,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -263,6 +264,25 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -821,19 +841,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15">
-      <x:c r="A1" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>47</x:v>
+      <x:c r="A1" s="20" t="str">
+        <x:v>form_title</x:v>
+      </x:c>
+      <x:c r="B1" s="20" t="str">
+        <x:v>form_id</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
+        <x:v>version</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="s">
-        <x:v>48</x:v>
+      <x:c r="A2" t="str">
+        <x:v>Protocol NFC Complete</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>methodmesh_protocol_nfc_complete_example</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>2026090703</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
